--- a/Backend/srvdata/barcode.xlsx
+++ b/Backend/srvdata/barcode.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22800" windowHeight="8790"/>
+    <workbookView windowWidth="18090" windowHeight="12750"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="89">
   <si>
     <t>EPL</t>
   </si>
@@ -39,6 +39,9 @@
     <t>EZPL</t>
   </si>
   <si>
+    <t>SBPL</t>
+  </si>
+  <si>
     <t>EAN13</t>
   </si>
   <si>
@@ -51,6 +54,9 @@
     <t>E</t>
   </si>
   <si>
+    <t>B3</t>
+  </si>
+  <si>
     <t>E30_SWEDEN</t>
   </si>
   <si>
@@ -69,6 +75,9 @@
     <t>Q</t>
   </si>
   <si>
+    <t>BG</t>
+  </si>
+  <si>
     <t>CODE128</t>
   </si>
   <si>
@@ -106,6 +115,9 @@
   </si>
   <si>
     <t>B</t>
+  </si>
+  <si>
+    <t>B4</t>
   </si>
   <si>
     <t>UPCAITF14</t>
@@ -1336,8 +1348,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="16.8833333333333" customWidth="1"/>
@@ -1347,7 +1359,7 @@
     <col min="6" max="6" width="12.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="D1" t="s">
         <v>0</v>
       </c>
@@ -1357,433 +1369,463 @@
       <c r="G1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="F2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="F3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="28.5" spans="1:8">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
         <v>5</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E4" t="s">
         <v>4</v>
       </c>
-      <c r="E3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" ht="28.5" spans="1:7">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="F4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="H4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" ht="28.5" spans="1:7">
+    </row>
+    <row r="5" ht="28.5" spans="1:8">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F5">
         <v>128</v>
       </c>
       <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" ht="28.5" spans="1:8">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="6" ht="28.5" spans="1:7">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>10</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F6">
         <v>128</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" ht="28.5" spans="1:7">
+        <v>14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" ht="28.5" spans="1:8">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F7">
         <v>128</v>
       </c>
       <c r="G7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" ht="28.5" spans="1:7">
+        <v>14</v>
+      </c>
+      <c r="H7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" ht="28.5" spans="1:8">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" ht="28.5" spans="1:8">
+      <c r="A9" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" ht="28.5" spans="1:7">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" ht="42.75" spans="1:7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" ht="42.75" spans="1:8">
       <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
         <v>20</v>
       </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" t="s">
-        <v>17</v>
-      </c>
       <c r="E10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
-        <v>26</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D16">
         <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" ht="28.5" spans="1:7">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" ht="28.5" spans="1:8">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D17" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D18">
         <v>3</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F18">
         <v>39</v>
       </c>
       <c r="G18" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" ht="28.5" spans="1:7">
+        <v>44</v>
+      </c>
+      <c r="H18" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" ht="28.5" spans="1:8">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D19" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" ht="28.5" spans="1:7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" ht="28.5" spans="1:8">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" ht="42.75" spans="1:7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" ht="42.75" spans="1:8">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D21" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E22" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G22" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D23" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E23" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G23" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1805,10 +1847,10 @@
   <sheetData>
     <row r="1" ht="17.25" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:2">
@@ -1816,15 +1858,15 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" ht="15" spans="1:2">
       <c r="A3" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" ht="15" spans="1:2">
@@ -1832,7 +1874,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" ht="15" spans="1:2">
@@ -1840,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" ht="15" spans="1:2">
@@ -1848,79 +1890,79 @@
         <v>1</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" ht="15" spans="1:2">
       <c r="A7" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" ht="15" spans="1:2">
       <c r="A8" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" ht="15" spans="1:2">
       <c r="A9" s="5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" ht="15" spans="1:2">
       <c r="A10" s="5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" ht="15" spans="1:2">
       <c r="A11" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>4</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="12" ht="15" spans="1:2">
       <c r="A12" s="5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" ht="15" spans="1:2">
       <c r="A13" s="5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" ht="15" spans="1:2">
       <c r="A14" s="5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" ht="15" spans="1:2">
       <c r="A15" s="5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" ht="15" spans="1:2">
@@ -1928,103 +1970,103 @@
         <v>2</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" ht="26.25" spans="1:2">
       <c r="A17" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" ht="26.25" spans="1:2">
       <c r="A18" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" ht="15" spans="1:2">
       <c r="A19" s="5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" ht="15" spans="1:2">
       <c r="A20" s="5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" ht="15" spans="1:2">
       <c r="A21" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" ht="15" spans="1:2">
       <c r="A22" s="5" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" ht="15" spans="1:2">
       <c r="A23" s="5" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" ht="15" spans="1:2">
       <c r="A24" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" ht="15" spans="1:2">
       <c r="A25" s="5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" ht="15" spans="1:2">
       <c r="A26" s="5" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" ht="15" spans="1:2">
       <c r="A27" s="5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" ht="15" spans="1:2">
       <c r="A28" s="6" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" ht="15"/>

--- a/Backend/srvdata/barcode.xlsx
+++ b/Backend/srvdata/barcode.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tmaxbackend\tmaxBack\Backend\srvdata\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="18090" windowHeight="12750"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="90">
   <si>
     <t>EPL</t>
   </si>
@@ -40,6 +45,9 @@
   </si>
   <si>
     <t>SBPL</t>
+  </si>
+  <si>
+    <t>ZPL</t>
   </si>
   <si>
     <t>EAN13</t>
@@ -1348,8 +1356,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="16.8833333333333" customWidth="1"/>
@@ -1359,7 +1367,7 @@
     <col min="6" max="6" width="12.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="D1" t="s">
         <v>0</v>
       </c>
@@ -1372,459 +1380,528 @@
       <c r="H1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="F2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E3" t="s">
         <v>5</v>
       </c>
-      <c r="E2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="F3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="H3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" ht="28.5" spans="1:9">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
         <v>6</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E4" t="s">
         <v>5</v>
       </c>
-      <c r="E3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="F4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" ht="28.5" spans="1:8">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="H4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="I4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" ht="28.5" spans="1:8">
+    </row>
+    <row r="5" ht="28.5" spans="1:9">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5">
         <v>128</v>
       </c>
       <c r="G5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" ht="28.5" spans="1:8">
+        <v>16</v>
+      </c>
+      <c r="I5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" ht="28.5" spans="1:9">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6">
         <v>128</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" ht="28.5" spans="1:8">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" ht="28.5" spans="1:9">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7">
         <v>128</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" ht="28.5" spans="1:8">
+        <v>16</v>
+      </c>
+      <c r="I7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" ht="28.5" spans="1:9">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="8" t="s">
+    </row>
+    <row r="9" ht="28.5" spans="1:9">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
         <v>21</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" t="s">
         <v>20</v>
       </c>
-      <c r="E8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" ht="28.5" spans="1:8">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="8" t="s">
+    </row>
+    <row r="10" ht="42.75" spans="1:9">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" t="s">
         <v>21</v>
       </c>
-      <c r="D9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" ht="42.75" spans="1:8">
-      <c r="A10" t="s">
+      <c r="E10" t="s">
         <v>23</v>
       </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="I10" t="s">
         <v>24</v>
       </c>
-      <c r="D10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="F11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
         <v>27</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E12" t="s">
         <v>26</v>
       </c>
-      <c r="E11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G11" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="F12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="H12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" t="s">
         <v>26</v>
       </c>
-      <c r="E12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" t="s">
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E13" t="s">
+      <c r="D14" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" t="s">
-        <v>33</v>
-      </c>
       <c r="E14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>35</v>
+      </c>
+      <c r="I14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <v>35</v>
+      </c>
+      <c r="I15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16">
         <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" ht="28.5" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" ht="28.5" spans="1:9">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" t="s">
+        <v>42</v>
+      </c>
+      <c r="I17" t="s">
         <v>39</v>
       </c>
-      <c r="D17" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D18">
         <v>3</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F18">
         <v>39</v>
       </c>
       <c r="G18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H18" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" ht="28.5" spans="1:8">
+        <v>29</v>
+      </c>
+      <c r="I18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" ht="28.5" spans="1:9">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" t="s">
         <v>21</v>
       </c>
-      <c r="D19" t="s">
-        <v>20</v>
-      </c>
       <c r="E19" t="s">
+        <v>23</v>
+      </c>
+      <c r="I19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" ht="28.5" spans="1:9">
+      <c r="A20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="20" ht="28.5" spans="1:8">
-      <c r="A20" t="s">
-        <v>45</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="D20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" t="s">
+        <v>23</v>
+      </c>
+      <c r="I20" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="8" t="s">
+    </row>
+    <row r="21" ht="42.75" spans="1:9">
+      <c r="A21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" t="s">
         <v>21</v>
       </c>
-      <c r="D20" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" ht="42.75" spans="1:8">
-      <c r="A21" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="8" t="s">
+      <c r="E21" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" t="s">
         <v>48</v>
       </c>
-      <c r="D21" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D22" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22" t="s">
+        <v>52</v>
+      </c>
+      <c r="I22" t="s">
         <v>50</v>
       </c>
-      <c r="E22" t="s">
-        <v>50</v>
-      </c>
-      <c r="G22" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G23" t="s">
+        <v>54</v>
+      </c>
+      <c r="I23" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1847,10 +1924,10 @@
   <sheetData>
     <row r="1" ht="17.25" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:2">
@@ -1858,15 +1935,15 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" ht="15" spans="1:2">
       <c r="A3" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" ht="15" spans="1:2">
@@ -1874,7 +1951,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" ht="15" spans="1:2">
@@ -1882,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" ht="15" spans="1:2">
@@ -1890,79 +1967,79 @@
         <v>1</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" ht="15" spans="1:2">
       <c r="A7" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" ht="15" spans="1:2">
       <c r="A8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="9" ht="15" spans="1:2">
       <c r="A9" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" ht="15" spans="1:2">
       <c r="A10" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" ht="15" spans="1:2">
       <c r="A11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>5</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="12" ht="15" spans="1:2">
       <c r="A12" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" ht="15" spans="1:2">
       <c r="A13" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" ht="15" spans="1:2">
       <c r="A14" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" ht="15" spans="1:2">
       <c r="A15" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" ht="15" spans="1:2">
@@ -1970,103 +2047,103 @@
         <v>2</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" ht="26.25" spans="1:2">
       <c r="A17" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" ht="26.25" spans="1:2">
       <c r="A18" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" ht="15" spans="1:2">
       <c r="A19" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" ht="15" spans="1:2">
       <c r="A20" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" ht="15" spans="1:2">
       <c r="A21" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" ht="15" spans="1:2">
       <c r="A22" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" ht="15" spans="1:2">
       <c r="A23" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" ht="15" spans="1:2">
       <c r="A24" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" ht="15" spans="1:2">
       <c r="A25" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" ht="15" spans="1:2">
       <c r="A26" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" ht="15" spans="1:2">
       <c r="A27" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" ht="15" spans="1:2">
       <c r="A28" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" ht="15"/>
